--- a/solution_dates.xlsx
+++ b/solution_dates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B296"/>
+  <dimension ref="A1:B317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3968,6 +3968,258 @@
         </is>
       </c>
     </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>secretsantacycles</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>jupiter</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>mazemovement</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>avoidingtheapocalypse</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>catering</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>councilling</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>jobpostings</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>maxflow</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>mincostmaxflow</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>mincut</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>piano</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>thekingofthenorth</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>tourist</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>waif</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>almennirborgarar</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>fairbandwidthsharing</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>enemydivision</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>heatingup</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>hotdogs</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>treehopping</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/solution_dates.xlsx
+++ b/solution_dates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B317"/>
+  <dimension ref="A1:B349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4220,6 +4220,390 @@
         </is>
       </c>
     </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>artsandcomputing</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>brillianceofwings</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>chainslides</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>dependencyflood</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>aplusorminusb</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>busyroads</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>cursedcactuschallenge</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>dejavu2</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>easygoingworkplace</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>endangeredsafarizone</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>falsesanctum</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>fickettconjecturepolyomino</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>georgettemegeorgetteyou</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>hungrypiplups</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>imperfection</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>jauntthroughthegarden</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>keeptheordering</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>antidiagonalgame</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>galacticsabotage</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>helpeeveeplseh</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>heroleveling</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>intervalscheduling2</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>joiningpoints</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>keyitemrecovery</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>largedifferences</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>codenames</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>eastereggs</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>mapcolouring</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>stystiskogarleidangurinn</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>bookcircle</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>busplanning</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>indoorienteering</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
